--- a/Data/National Accounts/PSA-14TAS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-14TAS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405AD07D-34C1-47A5-B3BB-DF8F42205987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79919128-4C56-4B3E-875F-9E721D2D451E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="TAS" sheetId="14" r:id="rId1"/>
@@ -694,10 +694,10 @@
     <t>Table 15.7 Gross Value Added in Transportation and Storage, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -746,10 +746,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1213,7 +1215,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1223,7 +1225,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -2326,19 +2328,19 @@
         <v>156094.27347132447</v>
       </c>
       <c r="CW12" s="18">
-        <v>158660.51588675834</v>
+        <v>158385.74685367171</v>
       </c>
       <c r="CX12" s="18">
-        <v>139496.7061644271</v>
+        <v>139336.24323371262</v>
       </c>
       <c r="CY12" s="18">
-        <v>145038.00297817434</v>
+        <v>144995.52953508659</v>
       </c>
       <c r="CZ12" s="18">
-        <v>162507.71239861927</v>
+        <v>162825.1921881804</v>
       </c>
       <c r="DA12" s="18">
-        <v>167146.95711585321</v>
+        <v>166232.03791446018</v>
       </c>
       <c r="DB12" s="8"/>
       <c r="DC12" s="8"/>
@@ -2717,19 +2719,19 @@
         <v>11779.74631200132</v>
       </c>
       <c r="CW13" s="18">
-        <v>11995.889513042071</v>
+        <v>11930.174698373712</v>
       </c>
       <c r="CX13" s="18">
-        <v>15438.952137807326</v>
+        <v>15753.975144267653</v>
       </c>
       <c r="CY13" s="18">
-        <v>13735.187306990967</v>
+        <v>13793.716851704212</v>
       </c>
       <c r="CZ13" s="18">
-        <v>12899.846004352688</v>
+        <v>12903.260493946573</v>
       </c>
       <c r="DA13" s="18">
-        <v>14341.25637369996</v>
+        <v>14366.887841660289</v>
       </c>
       <c r="DB13" s="8"/>
       <c r="DC13" s="8"/>
@@ -3117,10 +3119,10 @@
         <v>43227.782540167012</v>
       </c>
       <c r="CZ14" s="18">
-        <v>36222.382414890788</v>
+        <v>35319.514098488464</v>
       </c>
       <c r="DA14" s="18">
-        <v>48018.553191220592</v>
+        <v>48820.007592972921</v>
       </c>
       <c r="DB14" s="8"/>
       <c r="DC14" s="8"/>
@@ -3499,19 +3501,19 @@
         <v>60481.673907085031</v>
       </c>
       <c r="CW15" s="18">
-        <v>70377.811540652663</v>
+        <v>70019.636775594234</v>
       </c>
       <c r="CX15" s="18">
-        <v>68133.730430200376</v>
+        <v>67708.538961413724</v>
       </c>
       <c r="CY15" s="18">
-        <v>66537.54875089397</v>
+        <v>66205.356897266</v>
       </c>
       <c r="CZ15" s="18">
-        <v>64386.050083792172</v>
+        <v>64449.682743181169</v>
       </c>
       <c r="DA15" s="18">
-        <v>76307.743820129166</v>
+        <v>74991.313681055224</v>
       </c>
       <c r="DB15" s="8"/>
       <c r="DC15" s="8"/>
@@ -3893,7 +3895,7 @@
         <v>10349.920658314857</v>
       </c>
       <c r="CX16" s="18">
-        <v>10938.776227524608</v>
+        <v>10864.587224320047</v>
       </c>
       <c r="CY16" s="18">
         <v>11799.895110491978</v>
@@ -3902,7 +3904,7 @@
         <v>10569.987877605807</v>
       </c>
       <c r="DA16" s="18">
-        <v>12220.111181298198</v>
+        <v>12295.159518134082</v>
       </c>
       <c r="DB16" s="8"/>
       <c r="DC16" s="8"/>
@@ -4461,19 +4463,19 @@
         <v>273743.65702552511</v>
       </c>
       <c r="CW18" s="19">
-        <v>295727.31209356879</v>
+        <v>295028.6534807554</v>
       </c>
       <c r="CX18" s="19">
-        <v>273779.27749053668</v>
+        <v>273434.45709429128</v>
       </c>
       <c r="CY18" s="19">
-        <v>280338.41668671824</v>
+        <v>280022.28093471576</v>
       </c>
       <c r="CZ18" s="19">
-        <v>286585.97877926077</v>
+        <v>286067.63740140246</v>
       </c>
       <c r="DA18" s="19">
-        <v>318034.6216822011</v>
+        <v>316705.40654828271</v>
       </c>
       <c r="DB18" s="8"/>
       <c r="DC18" s="8"/>
@@ -5034,7 +5036,7 @@
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -5254,7 +5256,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -6357,19 +6359,19 @@
         <v>104143.64069751254</v>
       </c>
       <c r="CW34" s="18">
-        <v>125317.63014853586</v>
+        <v>125100.60448293679</v>
       </c>
       <c r="CX34" s="18">
-        <v>108130.39191021764</v>
+        <v>108006.00962147192</v>
       </c>
       <c r="CY34" s="18">
-        <v>98913.576785966317</v>
+        <v>98884.610583398971</v>
       </c>
       <c r="CZ34" s="18">
-        <v>107233.00910374286</v>
+        <v>107442.50262661494</v>
       </c>
       <c r="DA34" s="18">
-        <v>130354.94849569496</v>
+        <v>129641.41923118883</v>
       </c>
       <c r="DB34" s="8"/>
       <c r="DC34" s="8"/>
@@ -6748,19 +6750,19 @@
         <v>9627.9238012308524</v>
       </c>
       <c r="CW35" s="18">
-        <v>10221.954898199878</v>
+        <v>10165.957894313402</v>
       </c>
       <c r="CX35" s="18">
-        <v>12844.711776813054</v>
+        <v>13106.800789391775</v>
       </c>
       <c r="CY35" s="18">
-        <v>13872.049019452736</v>
+        <v>13931.161770899169</v>
       </c>
       <c r="CZ35" s="18">
-        <v>10450.887244453106</v>
+        <v>10453.653513579964</v>
       </c>
       <c r="DA35" s="18">
-        <v>11052.598371153566</v>
+        <v>11072.352171911785</v>
       </c>
       <c r="DB35" s="8"/>
       <c r="DC35" s="8"/>
@@ -7148,10 +7150,10 @@
         <v>32513.365766015675</v>
       </c>
       <c r="CZ36" s="18">
-        <v>29831.07253751994</v>
+        <v>29087.512107674949</v>
       </c>
       <c r="DA36" s="18">
-        <v>34250.361573159258</v>
+        <v>34822.017760614632</v>
       </c>
       <c r="DB36" s="8"/>
       <c r="DC36" s="8"/>
@@ -7530,19 +7532,19 @@
         <v>51669.74800632424</v>
       </c>
       <c r="CW37" s="18">
-        <v>58316.687020033671</v>
+        <v>58019.895102025206</v>
       </c>
       <c r="CX37" s="18">
-        <v>60141.907426000289</v>
+        <v>59766.589271649565</v>
       </c>
       <c r="CY37" s="18">
-        <v>50268.56427380586</v>
+        <v>50017.596093299995</v>
       </c>
       <c r="CZ37" s="18">
-        <v>53882.42418350371</v>
+        <v>53935.676121472556</v>
       </c>
       <c r="DA37" s="18">
-        <v>61501.146053220858</v>
+        <v>60440.153312524839</v>
       </c>
       <c r="DB37" s="8"/>
       <c r="DC37" s="8"/>
@@ -7924,7 +7926,7 @@
         <v>10164.44467167424</v>
       </c>
       <c r="CX38" s="18">
-        <v>10668.983381015078</v>
+        <v>10596.624167719187</v>
       </c>
       <c r="CY38" s="18">
         <v>11199.682511326413</v>
@@ -7933,7 +7935,7 @@
         <v>10066.026894520814</v>
       </c>
       <c r="DA38" s="18">
-        <v>12012.442214902063</v>
+        <v>12086.215177863745</v>
       </c>
       <c r="DB38" s="8"/>
       <c r="DC38" s="8"/>
@@ -8492,19 +8494,19 @@
         <v>202747.07285771181</v>
       </c>
       <c r="CW40" s="19">
-        <v>237285.02314430996</v>
+        <v>236715.20855681595</v>
       </c>
       <c r="CX40" s="19">
-        <v>225637.0298422137</v>
+        <v>225327.05919840009</v>
       </c>
       <c r="CY40" s="19">
-        <v>206767.23835656699</v>
+        <v>206546.41672494024</v>
       </c>
       <c r="CZ40" s="19">
-        <v>211463.41996374042</v>
+        <v>210985.37126386323</v>
       </c>
       <c r="DA40" s="19">
-        <v>249171.49670813073</v>
+        <v>248062.15765410385</v>
       </c>
       <c r="DB40" s="8"/>
       <c r="DC40" s="8"/>
@@ -9073,7 +9075,7 @@
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CX47" s="4"/>
       <c r="CY47" s="4"/>
@@ -9097,7 +9099,7 @@
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CX50" s="4"/>
       <c r="CY50" s="4"/>
@@ -9883,19 +9885,19 @@
         <v>5.2322077890425902</v>
       </c>
       <c r="CS56" s="15">
-        <v>5.2841552091168467</v>
+        <v>5.1018236103289212</v>
       </c>
       <c r="CT56" s="15">
-        <v>8.6666883166917756</v>
+        <v>8.5416891266909829</v>
       </c>
       <c r="CU56" s="15">
-        <v>7.9788069275582529</v>
+        <v>7.9471860308515545</v>
       </c>
       <c r="CV56" s="15">
-        <v>4.1086958442924555</v>
+        <v>4.3120856179854883</v>
       </c>
       <c r="CW56" s="15">
-        <v>5.3488047619559893</v>
+        <v>4.9539123416436155</v>
       </c>
       <c r="CX56" s="17"/>
       <c r="CY56" s="17"/>
@@ -10262,19 +10264,19 @@
         <v>23.764161400831554</v>
       </c>
       <c r="CS57" s="15">
-        <v>12.815353939186537</v>
+        <v>12.197338904303237</v>
       </c>
       <c r="CT57" s="15">
-        <v>7.3528669678034646</v>
+        <v>9.5433409457308329</v>
       </c>
       <c r="CU57" s="15">
-        <v>14.698292630214496</v>
+        <v>15.187054719655819</v>
       </c>
       <c r="CV57" s="15">
-        <v>9.5086911269914225</v>
+        <v>9.5376772316446647</v>
       </c>
       <c r="CW57" s="15">
-        <v>19.551420993899441</v>
+        <v>20.424790121629528</v>
       </c>
       <c r="CX57" s="17"/>
       <c r="CY57" s="17"/>
@@ -10650,10 +10652,10 @@
         <v>8.3469199231829521</v>
       </c>
       <c r="CV58" s="15">
-        <v>-2.2274306835408595</v>
+        <v>-4.6644806279087163</v>
       </c>
       <c r="CW58" s="15">
-        <v>8.2884879990957785</v>
+        <v>10.095878676202801</v>
       </c>
       <c r="CX58" s="17"/>
       <c r="CY58" s="17"/>
@@ -11020,19 +11022,19 @@
         <v>5.120521401546867</v>
       </c>
       <c r="CS59" s="15">
-        <v>17.417694705135361</v>
+        <v>16.820119215161199</v>
       </c>
       <c r="CT59" s="15">
-        <v>15.512240469326201</v>
+        <v>14.791381375337423</v>
       </c>
       <c r="CU59" s="15">
-        <v>11.012983908777471</v>
+        <v>10.458746345270399</v>
       </c>
       <c r="CV59" s="15">
-        <v>6.4554697720589473</v>
+        <v>6.5606795906343365</v>
       </c>
       <c r="CW59" s="15">
-        <v>8.4258548961147568</v>
+        <v>7.1004037358758438</v>
       </c>
       <c r="CX59" s="17"/>
       <c r="CY59" s="17"/>
@@ -11402,7 +11404,7 @@
         <v>13.406505035531495</v>
       </c>
       <c r="CT60" s="15">
-        <v>16.036599356028589</v>
+        <v>15.249615559814771</v>
       </c>
       <c r="CU60" s="15">
         <v>11.803017473766261</v>
@@ -11411,7 +11413,7 @@
         <v>26.732818649005537</v>
       </c>
       <c r="CW60" s="15">
-        <v>18.069612171189718</v>
+        <v>18.79472243351421</v>
       </c>
       <c r="CX60" s="17"/>
       <c r="CY60" s="17"/>
@@ -11954,19 +11956,19 @@
         <v>6.5576825140538659</v>
       </c>
       <c r="CS62" s="15">
-        <v>9.8421962517307549</v>
+        <v>9.5826930089686329</v>
       </c>
       <c r="CT62" s="15">
-        <v>9.7858124029948357</v>
+        <v>9.6475390183839949</v>
       </c>
       <c r="CU62" s="15">
-        <v>9.2152403678052508</v>
+        <v>9.0920790738525028</v>
       </c>
       <c r="CV62" s="15">
-        <v>4.69136779031858</v>
+        <v>4.5020149543513241</v>
       </c>
       <c r="CW62" s="15">
-        <v>7.5432023612260082</v>
+        <v>7.3473382370778069</v>
       </c>
       <c r="CX62" s="17"/>
       <c r="CY62" s="17"/>
@@ -12531,7 +12533,7 @@
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CX69" s="4"/>
       <c r="CY69" s="4"/>
@@ -12555,7 +12557,7 @@
     </row>
     <row r="72" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CX72" s="4"/>
       <c r="CY72" s="4"/>
@@ -13340,19 +13342,19 @@
         <v>3.7134407193309897</v>
       </c>
       <c r="CS78" s="15">
-        <v>5.2867598986398008</v>
+        <v>5.1044237890382647</v>
       </c>
       <c r="CT78" s="15">
-        <v>8.0269902788883627</v>
+        <v>7.9027269329425138</v>
       </c>
       <c r="CU78" s="15">
-        <v>6.9043514390936451</v>
+        <v>6.8730451897420721</v>
       </c>
       <c r="CV78" s="15">
-        <v>2.9664494015563321</v>
+        <v>3.167607649404161</v>
       </c>
       <c r="CW78" s="15">
-        <v>4.0196406053868827</v>
+        <v>3.6297304613515138</v>
       </c>
       <c r="CX78" s="17"/>
       <c r="CY78" s="17"/>
@@ -13719,19 +13721,19 @@
         <v>43.251888472233134</v>
       </c>
       <c r="CS79" s="15">
-        <v>-2.4179674118488634</v>
+        <v>-2.9525326209999321</v>
       </c>
       <c r="CT79" s="15">
-        <v>6.4107677602017503</v>
+        <v>8.5820187415090601</v>
       </c>
       <c r="CU79" s="15">
-        <v>13.691731989103701</v>
+        <v>14.176204836998195</v>
       </c>
       <c r="CV79" s="15">
-        <v>8.5476730000402057</v>
+        <v>8.5764047306185347</v>
       </c>
       <c r="CW79" s="15">
-        <v>8.1260725685648083</v>
+        <v>8.9159751301488086</v>
       </c>
       <c r="CX79" s="17"/>
       <c r="CY79" s="17"/>
@@ -14107,10 +14109,10 @@
         <v>9.2667807371771005</v>
       </c>
       <c r="CV80" s="15">
-        <v>1.5852950889564852</v>
+        <v>-0.94678972251890059</v>
       </c>
       <c r="CW80" s="15">
-        <v>2.9643040058068948</v>
+        <v>4.6828313079560786</v>
       </c>
       <c r="CX80" s="17"/>
       <c r="CY80" s="17"/>
@@ -14477,19 +14479,19 @@
         <v>4.9046625662416687</v>
       </c>
       <c r="CS81" s="15">
-        <v>14.491492974550965</v>
+        <v>13.908809843324789</v>
       </c>
       <c r="CT81" s="15">
-        <v>13.472966354745481</v>
+        <v>12.764833438386503</v>
       </c>
       <c r="CU81" s="15">
-        <v>10.607512918903367</v>
+        <v>10.05529968845704</v>
       </c>
       <c r="CV81" s="15">
-        <v>4.2823436586310493</v>
+        <v>4.3854057791630225</v>
       </c>
       <c r="CW81" s="15">
-        <v>5.4606309032836862</v>
+        <v>4.1714281045212687</v>
       </c>
       <c r="CX81" s="17"/>
       <c r="CY81" s="17"/>
@@ -14859,7 +14861,7 @@
         <v>12.3376407090892</v>
       </c>
       <c r="CT82" s="15">
-        <v>15.817868725762807</v>
+        <v>15.032368405130981</v>
       </c>
       <c r="CU82" s="15">
         <v>11.6975429289798</v>
@@ -14868,7 +14870,7 @@
         <v>26.772671736631025</v>
       </c>
       <c r="CW82" s="15">
-        <v>18.180998597766276</v>
+        <v>18.906792926375985</v>
       </c>
       <c r="CX82" s="17"/>
       <c r="CY82" s="17"/>
@@ -15411,19 +15413,19 @@
         <v>6.411990612900766</v>
       </c>
       <c r="CS84" s="15">
-        <v>9.5258510572473085</v>
+        <v>9.262836448010205</v>
       </c>
       <c r="CT84" s="15">
-        <v>9.5846304536249249</v>
+        <v>9.4340877059317023</v>
       </c>
       <c r="CU84" s="15">
-        <v>8.8493830500633521</v>
+        <v>8.7331349511975702</v>
       </c>
       <c r="CV84" s="15">
-        <v>4.2991235252731741</v>
+        <v>4.06333777846109</v>
       </c>
       <c r="CW84" s="15">
-        <v>5.0093652799113784</v>
+        <v>4.7935023552001468</v>
       </c>
       <c r="CX84" s="17"/>
       <c r="CY84" s="17"/>
@@ -15975,7 +15977,7 @@
     </row>
     <row r="90" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:175" x14ac:dyDescent="0.2">
@@ -15985,7 +15987,7 @@
     </row>
     <row r="93" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:175" x14ac:dyDescent="0.2">
@@ -16774,19 +16776,19 @@
         <v>149.88363420547554</v>
       </c>
       <c r="CW99" s="15">
-        <v>126.60669987032311</v>
+        <v>126.60669987032307</v>
       </c>
       <c r="CX99" s="15">
-        <v>129.00786143478828</v>
+        <v>129.00786143478831</v>
       </c>
       <c r="CY99" s="15">
-        <v>146.63103659876151</v>
+        <v>146.63103659876157</v>
       </c>
       <c r="CZ99" s="15">
-        <v>151.54635103207889</v>
+        <v>151.54635103207886</v>
       </c>
       <c r="DA99" s="15">
-        <v>128.22448172834291</v>
+        <v>128.22448172834294</v>
       </c>
       <c r="DB99" s="8"/>
       <c r="DC99" s="8"/>
@@ -17168,13 +17170,13 @@
         <v>117.35416202192978</v>
       </c>
       <c r="CX100" s="15">
-        <v>120.19695269205909</v>
+        <v>120.19695269205906</v>
       </c>
       <c r="CY100" s="15">
-        <v>99.013399446110313</v>
+        <v>99.013399446110327</v>
       </c>
       <c r="CZ100" s="15">
-        <v>123.43302250437529</v>
+        <v>123.43302250437527</v>
       </c>
       <c r="DA100" s="15">
         <v>129.7546141831186</v>
@@ -17565,10 +17567,10 @@
         <v>132.95388380045995</v>
       </c>
       <c r="CZ101" s="15">
-        <v>121.42500866950795</v>
+        <v>121.42500866950789</v>
       </c>
       <c r="DA101" s="15">
-        <v>140.19867524216431</v>
+        <v>140.1986752421644</v>
       </c>
       <c r="DB101" s="8"/>
       <c r="DC101" s="8"/>
@@ -17947,16 +17949,16 @@
         <v>117.05432335315867</v>
       </c>
       <c r="CW102" s="15">
-        <v>120.68211542345608</v>
+        <v>120.68211542345615</v>
       </c>
       <c r="CX102" s="15">
-        <v>113.28827658822323</v>
+        <v>113.28827658822324</v>
       </c>
       <c r="CY102" s="15">
         <v>132.3641319622204</v>
       </c>
       <c r="CZ102" s="15">
-        <v>119.49360308013792</v>
+        <v>119.49360308013797</v>
       </c>
       <c r="DA102" s="15">
         <v>124.07532008280823</v>
@@ -18341,7 +18343,7 @@
         <v>101.8247527792393</v>
       </c>
       <c r="CX103" s="15">
-        <v>102.52875870994056</v>
+        <v>102.52875870994052</v>
       </c>
       <c r="CY103" s="15">
         <v>105.35919298210963</v>
@@ -18350,7 +18352,7 @@
         <v>105.00655311540356</v>
       </c>
       <c r="DA103" s="15">
-        <v>101.72878222996577</v>
+        <v>101.7287822299658</v>
       </c>
       <c r="DB103" s="8"/>
       <c r="DC103" s="8"/>
@@ -18909,19 +18911,19 @@
         <v>135.01731648556958</v>
       </c>
       <c r="CW105" s="15">
-        <v>124.62957340283374</v>
+        <v>124.63443108681508</v>
       </c>
       <c r="CX105" s="15">
-        <v>121.33614667857864</v>
+        <v>121.3500314019244</v>
       </c>
       <c r="CY105" s="15">
-        <v>135.58164190560927</v>
+        <v>135.57353614496446</v>
       </c>
       <c r="CZ105" s="15">
-        <v>135.52508458834231</v>
+        <v>135.58647961599178</v>
       </c>
       <c r="DA105" s="15">
-        <v>127.63683883744288</v>
+        <v>127.67179385333516</v>
       </c>
       <c r="DB105" s="8"/>
       <c r="DC105" s="8"/>
@@ -19122,7 +19124,7 @@
     </row>
     <row r="112" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
@@ -19132,7 +19134,7 @@
     </row>
     <row r="115" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="116" spans="1:179" x14ac:dyDescent="0.2">
@@ -19921,19 +19923,19 @@
         <v>57.022060407693587</v>
       </c>
       <c r="CW121" s="15">
-        <v>53.650951196742284</v>
+        <v>53.684869244065858</v>
       </c>
       <c r="CX121" s="15">
-        <v>50.952251552073321</v>
+        <v>50.957821744339938</v>
       </c>
       <c r="CY121" s="15">
-        <v>51.736756129380645</v>
+        <v>51.779997309889339</v>
       </c>
       <c r="CZ121" s="15">
-        <v>56.704697518990898</v>
+        <v>56.918424491236117</v>
       </c>
       <c r="DA121" s="15">
-        <v>52.556214235969655</v>
+        <v>52.487906577344013</v>
       </c>
       <c r="DB121" s="8"/>
       <c r="DC121" s="8"/>
@@ -20312,19 +20314,19 @@
         <v>4.3032033837784676</v>
       </c>
       <c r="CW122" s="15">
-        <v>4.0564023079635421</v>
+        <v>4.0437342466981478</v>
       </c>
       <c r="CX122" s="15">
-        <v>5.6391967570814341</v>
+        <v>5.7615178831814324</v>
       </c>
       <c r="CY122" s="15">
-        <v>4.8995023476715343</v>
+        <v>4.9259354668709632</v>
       </c>
       <c r="CZ122" s="15">
-        <v>4.5012132342624591</v>
+        <v>4.5105628204427273</v>
       </c>
       <c r="DA122" s="15">
-        <v>4.5093381021990071</v>
+        <v>4.5363569881052888</v>
       </c>
       <c r="DB122" s="8"/>
       <c r="DC122" s="8"/>
@@ -20703,19 +20705,19 @@
         <v>13.533680467950671</v>
       </c>
       <c r="CW123" s="15">
-        <v>14.994615878012185</v>
+        <v>15.030124691835534</v>
       </c>
       <c r="CX123" s="15">
-        <v>14.526706657684105</v>
+        <v>14.54502587318852</v>
       </c>
       <c r="CY123" s="15">
-        <v>15.419856846974566</v>
+        <v>15.437265347554652</v>
       </c>
       <c r="CZ123" s="15">
-        <v>12.63927236398073</v>
+        <v>12.346560561455284</v>
       </c>
       <c r="DA123" s="15">
-        <v>15.098530133993886</v>
+        <v>15.414958691439375</v>
       </c>
       <c r="DB123" s="8"/>
       <c r="DC123" s="8"/>
@@ -21094,19 +21096,19 @@
         <v>22.094274097260797</v>
       </c>
       <c r="CW124" s="15">
-        <v>23.798211616783291</v>
+        <v>23.733164880597464</v>
       </c>
       <c r="CX124" s="15">
-        <v>24.886372356123797</v>
+        <v>24.762255525851696</v>
       </c>
       <c r="CY124" s="15">
-        <v>23.734723744712639</v>
+        <v>23.642888943077025</v>
       </c>
       <c r="CZ124" s="15">
-        <v>22.466573681675026</v>
+        <v>22.52952599903746</v>
       </c>
       <c r="DA124" s="15">
-        <v>23.993533602256786</v>
+        <v>23.678570725511932</v>
       </c>
       <c r="DB124" s="8"/>
       <c r="DC124" s="8"/>
@@ -21485,19 +21487,19 @@
         <v>3.0467816433164767</v>
       </c>
       <c r="CW125" s="15">
-        <v>3.4998190004987153</v>
+        <v>3.5081069368029976</v>
       </c>
       <c r="CX125" s="15">
-        <v>3.9954726770373301</v>
+        <v>3.973378973438412</v>
       </c>
       <c r="CY125" s="15">
-        <v>4.2091609312606311</v>
+        <v>4.2139129326080296</v>
       </c>
       <c r="CZ125" s="15">
-        <v>3.6882432010908692</v>
+        <v>3.6949261278283929</v>
       </c>
       <c r="DA125" s="15">
-        <v>3.8423839255806715</v>
+        <v>3.8822070175993808</v>
       </c>
       <c r="DB125" s="8"/>
       <c r="DC125" s="8"/>
@@ -22629,7 +22631,7 @@
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="136" spans="1:179" x14ac:dyDescent="0.2">
@@ -22639,7 +22641,7 @@
     </row>
     <row r="137" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="138" spans="1:179" x14ac:dyDescent="0.2">
@@ -23428,19 +23430,19 @@
         <v>51.366285702482472</v>
       </c>
       <c r="CW143" s="15">
-        <v>52.813122584783301</v>
+        <v>52.848570755397986</v>
       </c>
       <c r="CX143" s="15">
-        <v>47.922272326413989</v>
+        <v>47.932995711080054</v>
       </c>
       <c r="CY143" s="15">
-        <v>47.838128308988367</v>
+        <v>47.87524864935542</v>
       </c>
       <c r="CZ143" s="15">
-        <v>50.709956890950721</v>
+        <v>50.924147955378785</v>
       </c>
       <c r="DA143" s="15">
-        <v>52.315353167536415</v>
+        <v>52.261667179384908</v>
       </c>
       <c r="DB143" s="8"/>
       <c r="DC143" s="8"/>
@@ -23819,19 +23821,19 @@
         <v>4.748736277927792</v>
       </c>
       <c r="CW144" s="15">
-        <v>4.3078803553409175</v>
+        <v>4.2945943170666139</v>
       </c>
       <c r="CX144" s="15">
-        <v>5.6926435283230177</v>
+        <v>5.81678953074662</v>
       </c>
       <c r="CY144" s="15">
-        <v>6.7090169263326889</v>
+        <v>6.7448092258368373</v>
       </c>
       <c r="CZ144" s="15">
-        <v>4.9421726207989627</v>
+        <v>4.9546816686671518</v>
       </c>
       <c r="DA144" s="15">
-        <v>4.4357394473975997</v>
+        <v>4.4635394115014488</v>
       </c>
       <c r="DB144" s="8"/>
       <c r="DC144" s="8"/>
@@ -24210,19 +24212,19 @@
         <v>14.483830334900269</v>
       </c>
       <c r="CW145" s="15">
-        <v>14.018713008126049</v>
+        <v>14.052458483199759</v>
       </c>
       <c r="CX145" s="15">
-        <v>15.002429065760802</v>
+        <v>15.023067122338762</v>
       </c>
       <c r="CY145" s="15">
-        <v>15.724621571792174</v>
+        <v>15.741432982259878</v>
       </c>
       <c r="CZ145" s="15">
-        <v>14.106965896340402</v>
+        <v>13.786506587367816</v>
       </c>
       <c r="DA145" s="15">
-        <v>13.745698053609528</v>
+        <v>14.037617865587629</v>
       </c>
       <c r="DB145" s="8"/>
       <c r="DC145" s="8"/>
@@ -24601,19 +24603,19 @@
         <v>25.484830571431306</v>
       </c>
       <c r="CW146" s="15">
-        <v>24.576640466923667</v>
+        <v>24.510421386000374</v>
       </c>
       <c r="CX146" s="15">
-        <v>26.654271893251334</v>
+        <v>26.524372831327454</v>
       </c>
       <c r="CY146" s="15">
-        <v>24.311667879956143</v>
+        <v>24.216152904704654</v>
       </c>
       <c r="CZ146" s="15">
-        <v>25.480730517241668</v>
+        <v>25.563704155592543</v>
       </c>
       <c r="DA146" s="15">
-        <v>24.682255741819773</v>
+        <v>24.36492284196051</v>
       </c>
       <c r="DB146" s="8"/>
       <c r="DC146" s="8"/>
@@ -24992,19 +24994,19 @@
         <v>3.9163171132581551</v>
       </c>
       <c r="CW147" s="15">
-        <v>4.2836435848260495</v>
+        <v>4.2939550583352517</v>
       </c>
       <c r="CX147" s="15">
-        <v>4.7283831862508645</v>
+        <v>4.7027748045071132</v>
       </c>
       <c r="CY147" s="15">
-        <v>5.4165653129306346</v>
+        <v>5.4223562378432026</v>
       </c>
       <c r="CZ147" s="15">
-        <v>4.7601740746682486</v>
+        <v>4.7709596329937041</v>
       </c>
       <c r="DA147" s="15">
-        <v>4.8209535896366766</v>
+        <v>4.8722527015655004</v>
       </c>
       <c r="DB147" s="8"/>
       <c r="DC147" s="8"/>

--- a/Data/National Accounts/PSA-14TAS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-14TAS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79919128-4C56-4B3E-875F-9E721D2D451E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC09E4DF-038F-4BC1-A8F2-3C40026A4838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="TAS" sheetId="14" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TAS!$A$1:$DA$152</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TAS!$A$1:$DB$152</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="57">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -694,10 +694,13 @@
     <t>Table 15.7 Gross Value Added in Transportation and Storage, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1199,8 +1202,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="3" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="3"/>
+    <col min="2" max="106" width="13" style="3" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1331,6 +1334,7 @@
       <c r="CY6" s="20"/>
       <c r="CZ6" s="20"/>
       <c r="DA6" s="20"/>
+      <c r="DB6" s="20"/>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -1440,6 +1444,7 @@
       <c r="CY7" s="20"/>
       <c r="CZ7" s="20"/>
       <c r="DA7" s="20"/>
+      <c r="DB7" s="20"/>
     </row>
     <row r="8" spans="1:179" x14ac:dyDescent="0.2">
       <c r="B8" s="20"/>
@@ -1546,6 +1551,7 @@
       <c r="CY8" s="20"/>
       <c r="CZ8" s="20"/>
       <c r="DA8" s="20"/>
+      <c r="DB8" s="20"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
@@ -1705,6 +1711,9 @@
       <c r="CY9" s="22"/>
       <c r="CZ9" s="22"/>
       <c r="DA9" s="22"/>
+      <c r="DB9" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -2021,6 +2030,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2342,7 +2354,9 @@
       <c r="DA12" s="18">
         <v>166232.03791446018</v>
       </c>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="18">
+        <v>146645.0312596868</v>
+      </c>
       <c r="DC12" s="8"/>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
@@ -2733,7 +2747,9 @@
       <c r="DA13" s="18">
         <v>14366.887841660289</v>
       </c>
-      <c r="DB13" s="8"/>
+      <c r="DB13" s="18">
+        <v>16327.507426351</v>
+      </c>
       <c r="DC13" s="8"/>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
@@ -3124,7 +3140,9 @@
       <c r="DA14" s="18">
         <v>48820.007592972921</v>
       </c>
-      <c r="DB14" s="8"/>
+      <c r="DB14" s="18">
+        <v>44270.17836705927</v>
+      </c>
       <c r="DC14" s="8"/>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
@@ -3515,7 +3533,9 @@
       <c r="DA15" s="18">
         <v>74991.313681055224</v>
       </c>
-      <c r="DB15" s="8"/>
+      <c r="DB15" s="18">
+        <v>71762.217135857005</v>
+      </c>
       <c r="DC15" s="8"/>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
@@ -3906,7 +3926,9 @@
       <c r="DA16" s="18">
         <v>12295.159518134082</v>
       </c>
-      <c r="DB16" s="8"/>
+      <c r="DB16" s="18">
+        <v>12570.989323760754</v>
+      </c>
       <c r="DC16" s="8"/>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
@@ -4477,7 +4499,9 @@
       <c r="DA18" s="19">
         <v>316705.40654828271</v>
       </c>
-      <c r="DB18" s="8"/>
+      <c r="DB18" s="19">
+        <v>291575.9235127148</v>
+      </c>
       <c r="DC18" s="8"/>
       <c r="DD18" s="8"/>
       <c r="DE18" s="8"/>
@@ -4658,6 +4682,7 @@
       <c r="CY19" s="21"/>
       <c r="CZ19" s="21"/>
       <c r="DA19" s="21"/>
+      <c r="DB19" s="21"/>
     </row>
     <row r="20" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
@@ -5144,6 +5169,7 @@
       <c r="CY26" s="20"/>
       <c r="CZ26" s="20"/>
       <c r="DA26" s="20"/>
+      <c r="DB26" s="20"/>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
@@ -5253,6 +5279,7 @@
       <c r="CY27" s="20"/>
       <c r="CZ27" s="20"/>
       <c r="DA27" s="20"/>
+      <c r="DB27" s="20"/>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
@@ -5362,6 +5389,7 @@
       <c r="CY28" s="20"/>
       <c r="CZ28" s="20"/>
       <c r="DA28" s="20"/>
+      <c r="DB28" s="20"/>
     </row>
     <row r="29" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
@@ -5471,6 +5499,7 @@
       <c r="CY29" s="20"/>
       <c r="CZ29" s="20"/>
       <c r="DA29" s="20"/>
+      <c r="DB29" s="20"/>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
       <c r="B30" s="20"/>
@@ -5577,6 +5606,7 @@
       <c r="CY30" s="20"/>
       <c r="CZ30" s="20"/>
       <c r="DA30" s="20"/>
+      <c r="DB30" s="20"/>
     </row>
     <row r="31" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="16"/>
@@ -5736,6 +5766,9 @@
       <c r="CY31" s="22"/>
       <c r="CZ31" s="22"/>
       <c r="DA31" s="22"/>
+      <c r="DB31" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
@@ -6052,6 +6085,9 @@
       </c>
       <c r="DA32" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB32" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6373,7 +6409,9 @@
       <c r="DA34" s="18">
         <v>129641.41923118883</v>
       </c>
-      <c r="DB34" s="8"/>
+      <c r="DB34" s="18">
+        <v>111808.3909900978</v>
+      </c>
       <c r="DC34" s="8"/>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
@@ -6764,7 +6802,9 @@
       <c r="DA35" s="18">
         <v>11072.352171911785</v>
       </c>
-      <c r="DB35" s="8"/>
+      <c r="DB35" s="18">
+        <v>12816.73390986192</v>
+      </c>
       <c r="DC35" s="8"/>
       <c r="DD35" s="8"/>
       <c r="DE35" s="8"/>
@@ -7155,7 +7195,9 @@
       <c r="DA36" s="18">
         <v>34822.017760614632</v>
       </c>
-      <c r="DB36" s="8"/>
+      <c r="DB36" s="18">
+        <v>36396.44323017342</v>
+      </c>
       <c r="DC36" s="8"/>
       <c r="DD36" s="8"/>
       <c r="DE36" s="8"/>
@@ -7546,7 +7588,9 @@
       <c r="DA37" s="18">
         <v>60440.153312524839</v>
       </c>
-      <c r="DB37" s="8"/>
+      <c r="DB37" s="18">
+        <v>62103.270460716769</v>
+      </c>
       <c r="DC37" s="8"/>
       <c r="DD37" s="8"/>
       <c r="DE37" s="8"/>
@@ -7937,7 +7981,9 @@
       <c r="DA38" s="18">
         <v>12086.215177863745</v>
       </c>
-      <c r="DB38" s="8"/>
+      <c r="DB38" s="18">
+        <v>12153.472020587413</v>
+      </c>
       <c r="DC38" s="8"/>
       <c r="DD38" s="8"/>
       <c r="DE38" s="8"/>
@@ -8508,7 +8554,9 @@
       <c r="DA40" s="19">
         <v>248062.15765410385</v>
       </c>
-      <c r="DB40" s="8"/>
+      <c r="DB40" s="19">
+        <v>235278.31061143734</v>
+      </c>
       <c r="DC40" s="8"/>
       <c r="DD40" s="8"/>
       <c r="DE40" s="8"/>
@@ -8689,6 +8737,7 @@
       <c r="CY41" s="10"/>
       <c r="CZ41" s="10"/>
       <c r="DA41" s="10"/>
+      <c r="DB41" s="10"/>
     </row>
     <row r="42" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
@@ -8980,7 +9029,7 @@
       <c r="CY44" s="7"/>
       <c r="CZ44" s="7"/>
       <c r="DA44" s="7"/>
-      <c r="DB44" s="8"/>
+      <c r="DB44" s="7"/>
       <c r="DC44" s="8"/>
       <c r="DD44" s="8"/>
       <c r="DE44" s="8"/>
@@ -9063,6 +9112,7 @@
       <c r="CY45" s="4"/>
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
+      <c r="DB45" s="4"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
@@ -9072,6 +9122,7 @@
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
+      <c r="DB46" s="4"/>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
@@ -9081,12 +9132,14 @@
       <c r="CY47" s="4"/>
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
+      <c r="DB47" s="4"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX48" s="4"/>
       <c r="CY48" s="4"/>
       <c r="CZ48" s="4"/>
       <c r="DA48" s="4"/>
+      <c r="DB48" s="4"/>
     </row>
     <row r="49" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
@@ -9096,6 +9149,7 @@
       <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
+      <c r="DB49" s="4"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -9105,6 +9159,7 @@
       <c r="CY50" s="4"/>
       <c r="CZ50" s="4"/>
       <c r="DA50" s="4"/>
+      <c r="DB50" s="4"/>
     </row>
     <row r="51" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
@@ -9114,6 +9169,7 @@
       <c r="CY51" s="4"/>
       <c r="CZ51" s="4"/>
       <c r="DA51" s="4"/>
+      <c r="DB51" s="4"/>
     </row>
     <row r="52" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
@@ -9121,6 +9177,7 @@
       <c r="CY52" s="4"/>
       <c r="CZ52" s="4"/>
       <c r="DA52" s="4"/>
+      <c r="DB52" s="4"/>
     </row>
     <row r="53" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="16"/>
@@ -9274,10 +9331,13 @@
       <c r="CU53" s="22"/>
       <c r="CV53" s="22"/>
       <c r="CW53" s="22"/>
-      <c r="CX53" s="23"/>
+      <c r="CX53" s="22" t="s">
+        <v>56</v>
+      </c>
       <c r="CY53" s="23"/>
       <c r="CZ53" s="23"/>
       <c r="DA53" s="23"/>
+      <c r="DB53" s="23"/>
     </row>
     <row r="54" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
@@ -9583,17 +9643,20 @@
       <c r="CW54" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX54" s="24"/>
+      <c r="CX54" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY54" s="24"/>
       <c r="CZ54" s="24"/>
       <c r="DA54" s="24"/>
+      <c r="DB54" s="24"/>
     </row>
     <row r="55" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
-      <c r="CX55" s="4"/>
       <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
+      <c r="DB55" s="4"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
@@ -9899,11 +9962,13 @@
       <c r="CW56" s="15">
         <v>4.9539123416436155</v>
       </c>
-      <c r="CX56" s="17"/>
+      <c r="CX56" s="15">
+        <v>5.2454320974586182</v>
+      </c>
       <c r="CY56" s="17"/>
       <c r="CZ56" s="17"/>
       <c r="DA56" s="17"/>
-      <c r="DB56" s="8"/>
+      <c r="DB56" s="17"/>
       <c r="DC56" s="8"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
@@ -10278,11 +10343,13 @@
       <c r="CW57" s="15">
         <v>20.424790121629528</v>
       </c>
-      <c r="CX57" s="17"/>
+      <c r="CX57" s="15">
+        <v>3.6405559665493996</v>
+      </c>
       <c r="CY57" s="17"/>
       <c r="CZ57" s="17"/>
       <c r="DA57" s="17"/>
-      <c r="DB57" s="8"/>
+      <c r="DB57" s="17"/>
       <c r="DC57" s="8"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
@@ -10657,11 +10724,13 @@
       <c r="CW58" s="15">
         <v>10.095878676202801</v>
       </c>
-      <c r="CX58" s="17"/>
+      <c r="CX58" s="15">
+        <v>11.312396234887885</v>
+      </c>
       <c r="CY58" s="17"/>
       <c r="CZ58" s="17"/>
       <c r="DA58" s="17"/>
-      <c r="DB58" s="8"/>
+      <c r="DB58" s="17"/>
       <c r="DC58" s="8"/>
       <c r="DD58" s="8"/>
       <c r="DE58" s="8"/>
@@ -11036,11 +11105,13 @@
       <c r="CW59" s="15">
         <v>7.1004037358758438</v>
       </c>
-      <c r="CX59" s="17"/>
+      <c r="CX59" s="15">
+        <v>5.9869526600676153</v>
+      </c>
       <c r="CY59" s="17"/>
       <c r="CZ59" s="17"/>
       <c r="DA59" s="17"/>
-      <c r="DB59" s="8"/>
+      <c r="DB59" s="17"/>
       <c r="DC59" s="8"/>
       <c r="DD59" s="8"/>
       <c r="DE59" s="8"/>
@@ -11415,11 +11486,13 @@
       <c r="CW60" s="15">
         <v>18.79472243351421</v>
       </c>
-      <c r="CX60" s="17"/>
+      <c r="CX60" s="15">
+        <v>15.70609231817825</v>
+      </c>
       <c r="CY60" s="17"/>
       <c r="CZ60" s="17"/>
       <c r="DA60" s="17"/>
-      <c r="DB60" s="8"/>
+      <c r="DB60" s="17"/>
       <c r="DC60" s="8"/>
       <c r="DD60" s="8"/>
       <c r="DE60" s="8"/>
@@ -11591,11 +11664,11 @@
       <c r="CU61" s="8"/>
       <c r="CV61" s="8"/>
       <c r="CW61" s="8"/>
-      <c r="CX61" s="7"/>
+      <c r="CX61" s="8"/>
       <c r="CY61" s="7"/>
       <c r="CZ61" s="7"/>
       <c r="DA61" s="7"/>
-      <c r="DB61" s="8"/>
+      <c r="DB61" s="7"/>
       <c r="DC61" s="8"/>
       <c r="DD61" s="8"/>
       <c r="DE61" s="8"/>
@@ -11970,11 +12043,13 @@
       <c r="CW62" s="15">
         <v>7.3473382370778069</v>
       </c>
-      <c r="CX62" s="17"/>
+      <c r="CX62" s="15">
+        <v>6.6346672658623902</v>
+      </c>
       <c r="CY62" s="17"/>
       <c r="CZ62" s="17"/>
       <c r="DA62" s="17"/>
-      <c r="DB62" s="8"/>
+      <c r="DB62" s="17"/>
       <c r="DC62" s="8"/>
       <c r="DD62" s="8"/>
       <c r="DE62" s="8"/>
@@ -12147,19 +12222,20 @@
       <c r="CU63" s="10"/>
       <c r="CV63" s="10"/>
       <c r="CW63" s="10"/>
-      <c r="CX63" s="25"/>
+      <c r="CX63" s="10"/>
       <c r="CY63" s="25"/>
       <c r="CZ63" s="25"/>
       <c r="DA63" s="25"/>
+      <c r="DB63" s="25"/>
     </row>
     <row r="64" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A64" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX64" s="4"/>
       <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
+      <c r="DB64" s="4"/>
     </row>
     <row r="65" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="8"/>
@@ -12262,11 +12338,11 @@
       <c r="CU65" s="8"/>
       <c r="CV65" s="8"/>
       <c r="CW65" s="8"/>
-      <c r="CX65" s="7"/>
+      <c r="CX65" s="8"/>
       <c r="CY65" s="7"/>
       <c r="CZ65" s="7"/>
       <c r="DA65" s="7"/>
-      <c r="DB65" s="8"/>
+      <c r="DB65" s="7"/>
       <c r="DC65" s="8"/>
       <c r="DD65" s="8"/>
       <c r="DE65" s="8"/>
@@ -12438,11 +12514,11 @@
       <c r="CU66" s="8"/>
       <c r="CV66" s="8"/>
       <c r="CW66" s="8"/>
-      <c r="CX66" s="7"/>
+      <c r="CX66" s="8"/>
       <c r="CY66" s="7"/>
       <c r="CZ66" s="7"/>
       <c r="DA66" s="7"/>
-      <c r="DB66" s="8"/>
+      <c r="DB66" s="7"/>
       <c r="DC66" s="8"/>
       <c r="DD66" s="8"/>
       <c r="DE66" s="8"/>
@@ -12517,67 +12593,67 @@
       <c r="A67" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX67" s="4"/>
       <c r="CY67" s="4"/>
       <c r="CZ67" s="4"/>
       <c r="DA67" s="4"/>
+      <c r="DB67" s="4"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX68" s="4"/>
       <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
+      <c r="DB68" s="4"/>
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="CX69" s="4"/>
       <c r="CY69" s="4"/>
       <c r="CZ69" s="4"/>
       <c r="DA69" s="4"/>
+      <c r="DB69" s="4"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX70" s="4"/>
       <c r="CY70" s="4"/>
       <c r="CZ70" s="4"/>
       <c r="DA70" s="4"/>
+      <c r="DB70" s="4"/>
     </row>
     <row r="71" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="CX71" s="4"/>
       <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
+      <c r="DB71" s="4"/>
     </row>
     <row r="72" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="CX72" s="4"/>
       <c r="CY72" s="4"/>
       <c r="CZ72" s="4"/>
       <c r="DA72" s="4"/>
+      <c r="DB72" s="4"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX73" s="4"/>
       <c r="CY73" s="4"/>
       <c r="CZ73" s="4"/>
       <c r="DA73" s="4"/>
+      <c r="DB73" s="4"/>
     </row>
     <row r="74" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX74" s="4"/>
       <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
+      <c r="DB74" s="4"/>
     </row>
     <row r="75" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16"/>
@@ -12731,10 +12807,13 @@
       <c r="CU75" s="22"/>
       <c r="CV75" s="22"/>
       <c r="CW75" s="22"/>
-      <c r="CX75" s="23"/>
+      <c r="CX75" s="22" t="s">
+        <v>56</v>
+      </c>
       <c r="CY75" s="23"/>
       <c r="CZ75" s="23"/>
       <c r="DA75" s="23"/>
+      <c r="DB75" s="23"/>
     </row>
     <row r="76" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
@@ -13040,17 +13119,20 @@
       <c r="CW76" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX76" s="24"/>
+      <c r="CX76" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY76" s="24"/>
       <c r="CZ76" s="24"/>
       <c r="DA76" s="24"/>
+      <c r="DB76" s="24"/>
     </row>
     <row r="77" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
-      <c r="CX77" s="4"/>
       <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
+      <c r="DB77" s="4"/>
     </row>
     <row r="78" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
@@ -13356,11 +13438,13 @@
       <c r="CW78" s="15">
         <v>3.6297304613515138</v>
       </c>
-      <c r="CX78" s="17"/>
+      <c r="CX78" s="15">
+        <v>3.5205275909665232</v>
+      </c>
       <c r="CY78" s="17"/>
       <c r="CZ78" s="17"/>
       <c r="DA78" s="17"/>
-      <c r="DB78" s="8"/>
+      <c r="DB78" s="17"/>
       <c r="DC78" s="8"/>
       <c r="DD78" s="8"/>
       <c r="DE78" s="8"/>
@@ -13735,11 +13819,13 @@
       <c r="CW79" s="15">
         <v>8.9159751301488086</v>
       </c>
-      <c r="CX79" s="17"/>
+      <c r="CX79" s="15">
+        <v>-2.2131020696112671</v>
+      </c>
       <c r="CY79" s="17"/>
       <c r="CZ79" s="17"/>
       <c r="DA79" s="17"/>
-      <c r="DB79" s="8"/>
+      <c r="DB79" s="17"/>
       <c r="DC79" s="8"/>
       <c r="DD79" s="8"/>
       <c r="DE79" s="8"/>
@@ -14114,11 +14200,13 @@
       <c r="CW80" s="15">
         <v>4.6828313079560786</v>
       </c>
-      <c r="CX80" s="17"/>
+      <c r="CX80" s="15">
+        <v>7.5194387876929625</v>
+      </c>
       <c r="CY80" s="17"/>
       <c r="CZ80" s="17"/>
       <c r="DA80" s="17"/>
-      <c r="DB80" s="8"/>
+      <c r="DB80" s="17"/>
       <c r="DC80" s="8"/>
       <c r="DD80" s="8"/>
       <c r="DE80" s="8"/>
@@ -14493,11 +14581,13 @@
       <c r="CW81" s="15">
         <v>4.1714281045212687</v>
       </c>
-      <c r="CX81" s="17"/>
+      <c r="CX81" s="15">
+        <v>3.9096779949188374</v>
+      </c>
       <c r="CY81" s="17"/>
       <c r="CZ81" s="17"/>
       <c r="DA81" s="17"/>
-      <c r="DB81" s="8"/>
+      <c r="DB81" s="17"/>
       <c r="DC81" s="8"/>
       <c r="DD81" s="8"/>
       <c r="DE81" s="8"/>
@@ -14872,11 +14962,13 @@
       <c r="CW82" s="15">
         <v>18.906792926375985</v>
       </c>
-      <c r="CX82" s="17"/>
+      <c r="CX82" s="15">
+        <v>14.691922901360414</v>
+      </c>
       <c r="CY82" s="17"/>
       <c r="CZ82" s="17"/>
       <c r="DA82" s="17"/>
-      <c r="DB82" s="8"/>
+      <c r="DB82" s="17"/>
       <c r="DC82" s="8"/>
       <c r="DD82" s="8"/>
       <c r="DE82" s="8"/>
@@ -15048,11 +15140,11 @@
       <c r="CU83" s="8"/>
       <c r="CV83" s="8"/>
       <c r="CW83" s="8"/>
-      <c r="CX83" s="7"/>
+      <c r="CX83" s="8"/>
       <c r="CY83" s="7"/>
       <c r="CZ83" s="7"/>
       <c r="DA83" s="7"/>
-      <c r="DB83" s="8"/>
+      <c r="DB83" s="7"/>
       <c r="DC83" s="8"/>
       <c r="DD83" s="8"/>
       <c r="DE83" s="8"/>
@@ -15427,11 +15519,13 @@
       <c r="CW84" s="15">
         <v>4.7935023552001468</v>
       </c>
-      <c r="CX84" s="17"/>
+      <c r="CX84" s="15">
+        <v>4.4163588023732103</v>
+      </c>
       <c r="CY84" s="17"/>
       <c r="CZ84" s="17"/>
       <c r="DA84" s="17"/>
-      <c r="DB84" s="8"/>
+      <c r="DB84" s="17"/>
       <c r="DC84" s="8"/>
       <c r="DD84" s="8"/>
       <c r="DE84" s="8"/>
@@ -15604,19 +15698,20 @@
       <c r="CU85" s="10"/>
       <c r="CV85" s="10"/>
       <c r="CW85" s="10"/>
-      <c r="CX85" s="25"/>
+      <c r="CX85" s="10"/>
       <c r="CY85" s="25"/>
       <c r="CZ85" s="25"/>
       <c r="DA85" s="25"/>
+      <c r="DB85" s="25"/>
     </row>
     <row r="86" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX86" s="4"/>
       <c r="CY86" s="4"/>
       <c r="CZ86" s="4"/>
       <c r="DA86" s="4"/>
+      <c r="DB86" s="4"/>
     </row>
     <row r="87" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="8"/>
@@ -15723,7 +15818,7 @@
       <c r="CY87" s="7"/>
       <c r="CZ87" s="7"/>
       <c r="DA87" s="7"/>
-      <c r="DB87" s="8"/>
+      <c r="DB87" s="7"/>
       <c r="DC87" s="8"/>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
@@ -15899,7 +15994,7 @@
       <c r="CY88" s="7"/>
       <c r="CZ88" s="7"/>
       <c r="DA88" s="7"/>
-      <c r="DB88" s="8"/>
+      <c r="DB88" s="7"/>
       <c r="DC88" s="8"/>
       <c r="DD88" s="8"/>
       <c r="DE88" s="8"/>
@@ -16153,6 +16248,9 @@
       <c r="CY96" s="22"/>
       <c r="CZ96" s="22"/>
       <c r="DA96" s="22"/>
+      <c r="DB96" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="97" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
@@ -16469,6 +16567,9 @@
       </c>
       <c r="DA97" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB97" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -16790,7 +16891,9 @@
       <c r="DA99" s="15">
         <v>128.22448172834294</v>
       </c>
-      <c r="DB99" s="8"/>
+      <c r="DB99" s="15">
+        <v>131.15744709417584</v>
+      </c>
       <c r="DC99" s="8"/>
       <c r="DD99" s="8"/>
       <c r="DE99" s="8"/>
@@ -17181,7 +17284,9 @@
       <c r="DA100" s="15">
         <v>129.7546141831186</v>
       </c>
-      <c r="DB100" s="8"/>
+      <c r="DB100" s="15">
+        <v>127.39210739007146</v>
+      </c>
       <c r="DC100" s="8"/>
       <c r="DD100" s="8"/>
       <c r="DE100" s="8"/>
@@ -17572,7 +17677,9 @@
       <c r="DA101" s="15">
         <v>140.1986752421644</v>
       </c>
-      <c r="DB101" s="8"/>
+      <c r="DB101" s="15">
+        <v>121.63325434601356</v>
+      </c>
       <c r="DC101" s="8"/>
       <c r="DD101" s="8"/>
       <c r="DE101" s="8"/>
@@ -17963,7 +18070,9 @@
       <c r="DA102" s="15">
         <v>124.07532008280823</v>
       </c>
-      <c r="DB102" s="8"/>
+      <c r="DB102" s="15">
+        <v>115.5530402883532</v>
+      </c>
       <c r="DC102" s="8"/>
       <c r="DD102" s="8"/>
       <c r="DE102" s="8"/>
@@ -18354,7 +18463,9 @@
       <c r="DA103" s="15">
         <v>101.7287822299658</v>
       </c>
-      <c r="DB103" s="8"/>
+      <c r="DB103" s="15">
+        <v>103.43537470169912</v>
+      </c>
       <c r="DC103" s="8"/>
       <c r="DD103" s="8"/>
       <c r="DE103" s="8"/>
@@ -18925,7 +19036,9 @@
       <c r="DA105" s="15">
         <v>127.67179385333516</v>
       </c>
-      <c r="DB105" s="8"/>
+      <c r="DB105" s="15">
+        <v>123.92809296996911</v>
+      </c>
       <c r="DC105" s="8"/>
       <c r="DD105" s="8"/>
       <c r="DE105" s="8"/>
@@ -19106,6 +19219,7 @@
       <c r="CY106" s="10"/>
       <c r="CZ106" s="10"/>
       <c r="DA106" s="10"/>
+      <c r="DB106" s="10"/>
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="11" t="s">
@@ -19300,6 +19414,9 @@
       <c r="CY118" s="22"/>
       <c r="CZ118" s="22"/>
       <c r="DA118" s="22"/>
+      <c r="DB118" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="119" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
@@ -19616,6 +19733,9 @@
       </c>
       <c r="DA119" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB119" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -19937,7 +20057,9 @@
       <c r="DA121" s="15">
         <v>52.487906577344013</v>
       </c>
-      <c r="DB121" s="8"/>
+      <c r="DB121" s="15">
+        <v>50.293943852772202</v>
+      </c>
       <c r="DC121" s="8"/>
       <c r="DD121" s="8"/>
       <c r="DE121" s="8"/>
@@ -20328,7 +20450,9 @@
       <c r="DA122" s="15">
         <v>4.5363569881052888</v>
       </c>
-      <c r="DB122" s="8"/>
+      <c r="DB122" s="15">
+        <v>5.5997447353155696</v>
+      </c>
       <c r="DC122" s="8"/>
       <c r="DD122" s="8"/>
       <c r="DE122" s="8"/>
@@ -20719,7 +20843,9 @@
       <c r="DA123" s="15">
         <v>15.414958691439375</v>
       </c>
-      <c r="DB123" s="8"/>
+      <c r="DB123" s="15">
+        <v>15.183070616298252</v>
+      </c>
       <c r="DC123" s="8"/>
       <c r="DD123" s="8"/>
       <c r="DE123" s="8"/>
@@ -21110,7 +21236,9 @@
       <c r="DA124" s="15">
         <v>23.678570725511932</v>
       </c>
-      <c r="DB124" s="8"/>
+      <c r="DB124" s="15">
+        <v>24.611845954670418</v>
+      </c>
       <c r="DC124" s="8"/>
       <c r="DD124" s="8"/>
       <c r="DE124" s="8"/>
@@ -21501,7 +21629,9 @@
       <c r="DA125" s="15">
         <v>3.8822070175993808</v>
       </c>
-      <c r="DB125" s="8"/>
+      <c r="DB125" s="15">
+        <v>4.311394840943569</v>
+      </c>
       <c r="DC125" s="8"/>
       <c r="DD125" s="8"/>
       <c r="DE125" s="8"/>
@@ -22072,7 +22202,9 @@
       <c r="DA127" s="15">
         <v>100</v>
       </c>
-      <c r="DB127" s="8"/>
+      <c r="DB127" s="15">
+        <v>100</v>
+      </c>
       <c r="DC127" s="8"/>
       <c r="DD127" s="8"/>
       <c r="DE127" s="8"/>
@@ -22253,6 +22385,7 @@
       <c r="CY128" s="10"/>
       <c r="CZ128" s="10"/>
       <c r="DA128" s="10"/>
+      <c r="DB128" s="10"/>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A129" s="11" t="s">
@@ -22807,6 +22940,9 @@
       <c r="CY140" s="22"/>
       <c r="CZ140" s="22"/>
       <c r="DA140" s="22"/>
+      <c r="DB140" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="141" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
@@ -23123,6 +23259,9 @@
       </c>
       <c r="DA141" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB141" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -23444,7 +23583,9 @@
       <c r="DA143" s="15">
         <v>52.261667179384908</v>
       </c>
-      <c r="DB143" s="8"/>
+      <c r="DB143" s="15">
+        <v>47.521758677853484</v>
+      </c>
       <c r="DC143" s="8"/>
       <c r="DD143" s="8"/>
       <c r="DE143" s="8"/>
@@ -23835,7 +23976,9 @@
       <c r="DA144" s="15">
         <v>4.4635394115014488</v>
       </c>
-      <c r="DB144" s="8"/>
+      <c r="DB144" s="15">
+        <v>5.4474778727176361</v>
+      </c>
       <c r="DC144" s="8"/>
       <c r="DD144" s="8"/>
       <c r="DE144" s="8"/>
@@ -24226,7 +24369,9 @@
       <c r="DA145" s="15">
         <v>14.037617865587629</v>
       </c>
-      <c r="DB145" s="8"/>
+      <c r="DB145" s="15">
+        <v>15.469527614163392</v>
+      </c>
       <c r="DC145" s="8"/>
       <c r="DD145" s="8"/>
       <c r="DE145" s="8"/>
@@ -24617,7 +24762,9 @@
       <c r="DA146" s="15">
         <v>24.36492284196051</v>
       </c>
-      <c r="DB146" s="8"/>
+      <c r="DB146" s="15">
+        <v>26.395663203855818</v>
+      </c>
       <c r="DC146" s="8"/>
       <c r="DD146" s="8"/>
       <c r="DE146" s="8"/>
@@ -25008,7 +25155,9 @@
       <c r="DA147" s="15">
         <v>4.8722527015655004</v>
       </c>
-      <c r="DB147" s="8"/>
+      <c r="DB147" s="15">
+        <v>5.1655726314096579</v>
+      </c>
       <c r="DC147" s="8"/>
       <c r="DD147" s="8"/>
       <c r="DE147" s="8"/>
@@ -25579,7 +25728,9 @@
       <c r="DA149" s="15">
         <v>100</v>
       </c>
-      <c r="DB149" s="8"/>
+      <c r="DB149" s="15">
+        <v>100</v>
+      </c>
       <c r="DC149" s="8"/>
       <c r="DD149" s="8"/>
       <c r="DE149" s="8"/>
@@ -25760,6 +25911,7 @@
       <c r="CY150" s="10"/>
       <c r="CZ150" s="10"/>
       <c r="DA150" s="10"/>
+      <c r="DB150" s="10"/>
     </row>
     <row r="151" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A151" s="11" t="s">
@@ -25953,9 +26105,9 @@
   <pageSetup paperSize="9" scale="29" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="44" max="81" man="1"/>
-    <brk id="88" max="81" man="1"/>
-    <brk id="109" max="81" man="1"/>
+    <brk id="44" max="105" man="1"/>
+    <brk id="88" max="105" man="1"/>
+    <brk id="109" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-14TAS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-14TAS_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC09E4DF-038F-4BC1-A8F2-3C40026A4838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E0624A-9673-418E-9625-AF928CCC5818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TAS!$A$1:$DB$152</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TAS!$A$1:$DC$152</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="57">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -694,13 +694,13 @@
     <t>Table 15.7 Gross Value Added in Transportation and Storage, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1202,8 +1202,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="3" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="3"/>
+    <col min="2" max="107" width="13" style="3" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -1335,6 +1335,7 @@
       <c r="CZ6" s="20"/>
       <c r="DA6" s="20"/>
       <c r="DB6" s="20"/>
+      <c r="DC6" s="20"/>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -1445,6 +1446,7 @@
       <c r="CZ7" s="20"/>
       <c r="DA7" s="20"/>
       <c r="DB7" s="20"/>
+      <c r="DC7" s="20"/>
     </row>
     <row r="8" spans="1:179" x14ac:dyDescent="0.2">
       <c r="B8" s="20"/>
@@ -1552,6 +1554,7 @@
       <c r="CZ8" s="20"/>
       <c r="DA8" s="20"/>
       <c r="DB8" s="20"/>
+      <c r="DC8" s="20"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
@@ -1714,6 +1717,7 @@
       <c r="DB9" s="22">
         <v>2026</v>
       </c>
+      <c r="DC9" s="22"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -2033,6 +2037,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2355,9 +2362,11 @@
         <v>166232.03791446018</v>
       </c>
       <c r="DB12" s="18">
-        <v>146645.0312596868</v>
-      </c>
-      <c r="DC12" s="8"/>
+        <v>146386.07817219332</v>
+      </c>
+      <c r="DC12" s="18">
+        <v>150370.54759406252</v>
+      </c>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
       <c r="DF12" s="8"/>
@@ -2748,9 +2757,11 @@
         <v>14366.887841660289</v>
       </c>
       <c r="DB13" s="18">
-        <v>16327.507426351</v>
-      </c>
-      <c r="DC13" s="8"/>
+        <v>16525.551480174199</v>
+      </c>
+      <c r="DC13" s="18">
+        <v>16698.829347931995</v>
+      </c>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
       <c r="DF13" s="8"/>
@@ -3141,9 +3152,11 @@
         <v>48820.007592972921</v>
       </c>
       <c r="DB14" s="18">
-        <v>44270.17836705927</v>
-      </c>
-      <c r="DC14" s="8"/>
+        <v>43889.779929668788</v>
+      </c>
+      <c r="DC14" s="18">
+        <v>47071.887960584514</v>
+      </c>
       <c r="DD14" s="8"/>
       <c r="DE14" s="8"/>
       <c r="DF14" s="8"/>
@@ -3534,9 +3547,11 @@
         <v>74991.313681055224</v>
       </c>
       <c r="DB15" s="18">
-        <v>71762.217135857005</v>
-      </c>
-      <c r="DC15" s="8"/>
+        <v>72435.352100100499</v>
+      </c>
+      <c r="DC15" s="18">
+        <v>73566.130337276059</v>
+      </c>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
       <c r="DF15" s="8"/>
@@ -3927,9 +3942,11 @@
         <v>12295.159518134082</v>
       </c>
       <c r="DB16" s="18">
-        <v>12570.989323760754</v>
-      </c>
-      <c r="DC16" s="8"/>
+        <v>13237.173509599488</v>
+      </c>
+      <c r="DC16" s="18">
+        <v>14805.001342639265</v>
+      </c>
       <c r="DD16" s="8"/>
       <c r="DE16" s="8"/>
       <c r="DF16" s="8"/>
@@ -4500,9 +4517,11 @@
         <v>316705.40654828271</v>
       </c>
       <c r="DB18" s="19">
-        <v>291575.9235127148</v>
-      </c>
-      <c r="DC18" s="8"/>
+        <v>292473.93519173627</v>
+      </c>
+      <c r="DC18" s="19">
+        <v>302512.39658249432</v>
+      </c>
       <c r="DD18" s="8"/>
       <c r="DE18" s="8"/>
       <c r="DF18" s="8"/>
@@ -4683,6 +4702,7 @@
       <c r="CZ19" s="21"/>
       <c r="DA19" s="21"/>
       <c r="DB19" s="21"/>
+      <c r="DC19" s="21"/>
     </row>
     <row r="20" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
@@ -5061,7 +5081,7 @@
     </row>
     <row r="25" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:179" x14ac:dyDescent="0.2">
@@ -5170,6 +5190,7 @@
       <c r="CZ26" s="20"/>
       <c r="DA26" s="20"/>
       <c r="DB26" s="20"/>
+      <c r="DC26" s="20"/>
     </row>
     <row r="27" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
@@ -5280,10 +5301,11 @@
       <c r="CZ27" s="20"/>
       <c r="DA27" s="20"/>
       <c r="DB27" s="20"/>
+      <c r="DC27" s="20"/>
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -5390,6 +5412,7 @@
       <c r="CZ28" s="20"/>
       <c r="DA28" s="20"/>
       <c r="DB28" s="20"/>
+      <c r="DC28" s="20"/>
     </row>
     <row r="29" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
@@ -5500,6 +5523,7 @@
       <c r="CZ29" s="20"/>
       <c r="DA29" s="20"/>
       <c r="DB29" s="20"/>
+      <c r="DC29" s="20"/>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
       <c r="B30" s="20"/>
@@ -5607,6 +5631,7 @@
       <c r="CZ30" s="20"/>
       <c r="DA30" s="20"/>
       <c r="DB30" s="20"/>
+      <c r="DC30" s="20"/>
     </row>
     <row r="31" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="16"/>
@@ -5769,6 +5794,7 @@
       <c r="DB31" s="22">
         <v>2026</v>
       </c>
+      <c r="DC31" s="22"/>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
@@ -6088,6 +6114,9 @@
       </c>
       <c r="DB32" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC32" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6410,9 +6439,11 @@
         <v>129641.41923118883</v>
       </c>
       <c r="DB34" s="18">
-        <v>111808.3909900978</v>
-      </c>
-      <c r="DC34" s="8"/>
+        <v>111602.99723487708</v>
+      </c>
+      <c r="DC34" s="18">
+        <v>101897.25098051212</v>
+      </c>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
       <c r="DF34" s="8"/>
@@ -6803,9 +6834,11 @@
         <v>11072.352171911785</v>
       </c>
       <c r="DB35" s="18">
-        <v>12816.73390986192</v>
-      </c>
-      <c r="DC35" s="8"/>
+        <v>12972.194132540231</v>
+      </c>
+      <c r="DC35" s="18">
+        <v>13426.706005763042</v>
+      </c>
       <c r="DD35" s="8"/>
       <c r="DE35" s="8"/>
       <c r="DF35" s="8"/>
@@ -7196,9 +7229,11 @@
         <v>34822.017760614632</v>
       </c>
       <c r="DB36" s="18">
-        <v>36396.44323017342</v>
-      </c>
-      <c r="DC36" s="8"/>
+        <v>36608.610776183952</v>
+      </c>
+      <c r="DC36" s="18">
+        <v>31903.668811166659</v>
+      </c>
       <c r="DD36" s="8"/>
       <c r="DE36" s="8"/>
       <c r="DF36" s="8"/>
@@ -7589,9 +7624,11 @@
         <v>60440.153312524839</v>
       </c>
       <c r="DB37" s="18">
-        <v>62103.270460716769</v>
-      </c>
-      <c r="DC37" s="8"/>
+        <v>62685.803782699251</v>
+      </c>
+      <c r="DC37" s="18">
+        <v>53162.712058730714</v>
+      </c>
       <c r="DD37" s="8"/>
       <c r="DE37" s="8"/>
       <c r="DF37" s="8"/>
@@ -7982,9 +8019,11 @@
         <v>12086.215177863745</v>
       </c>
       <c r="DB38" s="18">
-        <v>12153.472020587413</v>
-      </c>
-      <c r="DC38" s="8"/>
+        <v>12797.530388200972</v>
+      </c>
+      <c r="DC38" s="18">
+        <v>14029.066068632153</v>
+      </c>
       <c r="DD38" s="8"/>
       <c r="DE38" s="8"/>
       <c r="DF38" s="8"/>
@@ -8555,9 +8594,11 @@
         <v>248062.15765410385</v>
       </c>
       <c r="DB40" s="19">
-        <v>235278.31061143734</v>
-      </c>
-      <c r="DC40" s="8"/>
+        <v>236667.13631450149</v>
+      </c>
+      <c r="DC40" s="19">
+        <v>214419.40392480468</v>
+      </c>
       <c r="DD40" s="8"/>
       <c r="DE40" s="8"/>
       <c r="DF40" s="8"/>
@@ -8738,6 +8779,7 @@
       <c r="CZ41" s="10"/>
       <c r="DA41" s="10"/>
       <c r="DB41" s="10"/>
+      <c r="DC41" s="10"/>
     </row>
     <row r="42" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
@@ -9030,7 +9072,7 @@
       <c r="CZ44" s="7"/>
       <c r="DA44" s="7"/>
       <c r="DB44" s="7"/>
-      <c r="DC44" s="8"/>
+      <c r="DC44" s="7"/>
       <c r="DD44" s="8"/>
       <c r="DE44" s="8"/>
       <c r="DF44" s="8"/>
@@ -9113,6 +9155,7 @@
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
       <c r="DB45" s="4"/>
+      <c r="DC45" s="4"/>
     </row>
     <row r="46" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
@@ -9123,16 +9166,18 @@
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
       <c r="DB46" s="4"/>
+      <c r="DC46" s="4"/>
     </row>
     <row r="47" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="CX47" s="4"/>
       <c r="CY47" s="4"/>
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
       <c r="DB47" s="4"/>
+      <c r="DC47" s="4"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX48" s="4"/>
@@ -9140,6 +9185,7 @@
       <c r="CZ48" s="4"/>
       <c r="DA48" s="4"/>
       <c r="DB48" s="4"/>
+      <c r="DC48" s="4"/>
     </row>
     <row r="49" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
@@ -9150,16 +9196,18 @@
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
       <c r="DB49" s="4"/>
+      <c r="DC49" s="4"/>
     </row>
     <row r="50" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="CX50" s="4"/>
       <c r="CY50" s="4"/>
       <c r="CZ50" s="4"/>
       <c r="DA50" s="4"/>
       <c r="DB50" s="4"/>
+      <c r="DC50" s="4"/>
     </row>
     <row r="51" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
@@ -9170,14 +9218,14 @@
       <c r="CZ51" s="4"/>
       <c r="DA51" s="4"/>
       <c r="DB51" s="4"/>
+      <c r="DC51" s="4"/>
     </row>
     <row r="52" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
-      <c r="CX52" s="4"/>
-      <c r="CY52" s="4"/>
       <c r="CZ52" s="4"/>
       <c r="DA52" s="4"/>
       <c r="DB52" s="4"/>
+      <c r="DC52" s="4"/>
     </row>
     <row r="53" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="16"/>
@@ -9332,12 +9380,13 @@
       <c r="CV53" s="22"/>
       <c r="CW53" s="22"/>
       <c r="CX53" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY53" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="CY53" s="22"/>
       <c r="CZ53" s="23"/>
       <c r="DA53" s="23"/>
       <c r="DB53" s="23"/>
+      <c r="DC53" s="23"/>
     </row>
     <row r="54" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
@@ -9646,17 +9695,20 @@
       <c r="CX54" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY54" s="24"/>
+      <c r="CY54" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ54" s="24"/>
       <c r="DA54" s="24"/>
       <c r="DB54" s="24"/>
+      <c r="DC54" s="24"/>
     </row>
     <row r="55" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6"/>
-      <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
       <c r="DB55" s="4"/>
+      <c r="DC55" s="4"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
@@ -9963,13 +10015,15 @@
         <v>4.9539123416436155</v>
       </c>
       <c r="CX56" s="15">
-        <v>5.2454320974586182</v>
-      </c>
-      <c r="CY56" s="17"/>
+        <v>5.0595844805832826</v>
+      </c>
+      <c r="CY56" s="15">
+        <v>3.7070232966563736</v>
+      </c>
       <c r="CZ56" s="17"/>
       <c r="DA56" s="17"/>
       <c r="DB56" s="17"/>
-      <c r="DC56" s="8"/>
+      <c r="DC56" s="17"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
       <c r="DF56" s="8"/>
@@ -10344,13 +10398,15 @@
         <v>20.424790121629528</v>
       </c>
       <c r="CX57" s="15">
-        <v>3.6405559665493996</v>
-      </c>
-      <c r="CY57" s="17"/>
+        <v>4.8976612495627734</v>
+      </c>
+      <c r="CY57" s="15">
+        <v>21.061128972419468</v>
+      </c>
       <c r="CZ57" s="17"/>
       <c r="DA57" s="17"/>
       <c r="DB57" s="17"/>
-      <c r="DC57" s="8"/>
+      <c r="DC57" s="17"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
       <c r="DF57" s="8"/>
@@ -10725,13 +10781,15 @@
         <v>10.095878676202801</v>
       </c>
       <c r="CX58" s="15">
-        <v>11.312396234887885</v>
-      </c>
-      <c r="CY58" s="17"/>
+        <v>10.355927046106657</v>
+      </c>
+      <c r="CY58" s="15">
+        <v>8.8926731711153053</v>
+      </c>
       <c r="CZ58" s="17"/>
       <c r="DA58" s="17"/>
       <c r="DB58" s="17"/>
-      <c r="DC58" s="8"/>
+      <c r="DC58" s="17"/>
       <c r="DD58" s="8"/>
       <c r="DE58" s="8"/>
       <c r="DF58" s="8"/>
@@ -11106,13 +11164,15 @@
         <v>7.1004037358758438</v>
       </c>
       <c r="CX59" s="15">
-        <v>5.9869526600676153</v>
-      </c>
-      <c r="CY59" s="17"/>
+        <v>6.981118203393109</v>
+      </c>
+      <c r="CY59" s="15">
+        <v>11.118093436807726</v>
+      </c>
       <c r="CZ59" s="17"/>
       <c r="DA59" s="17"/>
       <c r="DB59" s="17"/>
-      <c r="DC59" s="8"/>
+      <c r="DC59" s="17"/>
       <c r="DD59" s="8"/>
       <c r="DE59" s="8"/>
       <c r="DF59" s="8"/>
@@ -11487,13 +11547,15 @@
         <v>18.79472243351421</v>
       </c>
       <c r="CX60" s="15">
-        <v>15.70609231817825</v>
-      </c>
-      <c r="CY60" s="17"/>
+        <v>21.83779499665188</v>
+      </c>
+      <c r="CY60" s="15">
+        <v>25.467228344049204</v>
+      </c>
       <c r="CZ60" s="17"/>
       <c r="DA60" s="17"/>
       <c r="DB60" s="17"/>
-      <c r="DC60" s="8"/>
+      <c r="DC60" s="17"/>
       <c r="DD60" s="8"/>
       <c r="DE60" s="8"/>
       <c r="DF60" s="8"/>
@@ -11665,11 +11727,11 @@
       <c r="CV61" s="8"/>
       <c r="CW61" s="8"/>
       <c r="CX61" s="8"/>
-      <c r="CY61" s="7"/>
+      <c r="CY61" s="8"/>
       <c r="CZ61" s="7"/>
       <c r="DA61" s="7"/>
       <c r="DB61" s="7"/>
-      <c r="DC61" s="8"/>
+      <c r="DC61" s="7"/>
       <c r="DD61" s="8"/>
       <c r="DE61" s="8"/>
       <c r="DF61" s="8"/>
@@ -12044,13 +12106,15 @@
         <v>7.3473382370778069</v>
       </c>
       <c r="CX62" s="15">
-        <v>6.6346672658623902</v>
-      </c>
-      <c r="CY62" s="17"/>
+        <v>6.9630866203813468</v>
+      </c>
+      <c r="CY62" s="15">
+        <v>8.0315450515960407</v>
+      </c>
       <c r="CZ62" s="17"/>
       <c r="DA62" s="17"/>
       <c r="DB62" s="17"/>
-      <c r="DC62" s="8"/>
+      <c r="DC62" s="17"/>
       <c r="DD62" s="8"/>
       <c r="DE62" s="8"/>
       <c r="DF62" s="8"/>
@@ -12223,19 +12287,20 @@
       <c r="CV63" s="10"/>
       <c r="CW63" s="10"/>
       <c r="CX63" s="10"/>
-      <c r="CY63" s="25"/>
+      <c r="CY63" s="10"/>
       <c r="CZ63" s="25"/>
       <c r="DA63" s="25"/>
       <c r="DB63" s="25"/>
+      <c r="DC63" s="25"/>
     </row>
     <row r="64" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A64" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
       <c r="DB64" s="4"/>
+      <c r="DC64" s="4"/>
     </row>
     <row r="65" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="8"/>
@@ -12339,11 +12404,11 @@
       <c r="CV65" s="8"/>
       <c r="CW65" s="8"/>
       <c r="CX65" s="8"/>
-      <c r="CY65" s="7"/>
+      <c r="CY65" s="8"/>
       <c r="CZ65" s="7"/>
       <c r="DA65" s="7"/>
       <c r="DB65" s="7"/>
-      <c r="DC65" s="8"/>
+      <c r="DC65" s="7"/>
       <c r="DD65" s="8"/>
       <c r="DE65" s="8"/>
       <c r="DF65" s="8"/>
@@ -12515,11 +12580,11 @@
       <c r="CV66" s="8"/>
       <c r="CW66" s="8"/>
       <c r="CX66" s="8"/>
-      <c r="CY66" s="7"/>
+      <c r="CY66" s="8"/>
       <c r="CZ66" s="7"/>
       <c r="DA66" s="7"/>
       <c r="DB66" s="7"/>
-      <c r="DC66" s="8"/>
+      <c r="DC66" s="7"/>
       <c r="DD66" s="8"/>
       <c r="DE66" s="8"/>
       <c r="DF66" s="8"/>
@@ -12593,67 +12658,67 @@
       <c r="A67" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY67" s="4"/>
       <c r="CZ67" s="4"/>
       <c r="DA67" s="4"/>
       <c r="DB67" s="4"/>
+      <c r="DC67" s="4"/>
     </row>
     <row r="68" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
       <c r="DB68" s="4"/>
+      <c r="DC68" s="4"/>
     </row>
     <row r="69" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="CY69" s="4"/>
+        <v>56</v>
+      </c>
       <c r="CZ69" s="4"/>
       <c r="DA69" s="4"/>
       <c r="DB69" s="4"/>
+      <c r="DC69" s="4"/>
     </row>
     <row r="70" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY70" s="4"/>
       <c r="CZ70" s="4"/>
       <c r="DA70" s="4"/>
       <c r="DB70" s="4"/>
+      <c r="DC70" s="4"/>
     </row>
     <row r="71" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
       <c r="DB71" s="4"/>
+      <c r="DC71" s="4"/>
     </row>
     <row r="72" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="CY72" s="4"/>
+        <v>55</v>
+      </c>
       <c r="CZ72" s="4"/>
       <c r="DA72" s="4"/>
       <c r="DB72" s="4"/>
+      <c r="DC72" s="4"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY73" s="4"/>
       <c r="CZ73" s="4"/>
       <c r="DA73" s="4"/>
       <c r="DB73" s="4"/>
+      <c r="DC73" s="4"/>
     </row>
     <row r="74" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
       <c r="DB74" s="4"/>
+      <c r="DC74" s="4"/>
     </row>
     <row r="75" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16"/>
@@ -12808,12 +12873,13 @@
       <c r="CV75" s="22"/>
       <c r="CW75" s="22"/>
       <c r="CX75" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY75" s="23"/>
+        <v>54</v>
+      </c>
+      <c r="CY75" s="22"/>
       <c r="CZ75" s="23"/>
       <c r="DA75" s="23"/>
       <c r="DB75" s="23"/>
+      <c r="DC75" s="23"/>
     </row>
     <row r="76" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
@@ -13122,17 +13188,20 @@
       <c r="CX76" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY76" s="24"/>
+      <c r="CY76" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ76" s="24"/>
       <c r="DA76" s="24"/>
       <c r="DB76" s="24"/>
+      <c r="DC76" s="24"/>
     </row>
     <row r="77" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6"/>
-      <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
       <c r="DB77" s="4"/>
+      <c r="DC77" s="4"/>
     </row>
     <row r="78" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
@@ -13439,13 +13508,15 @@
         <v>3.6297304613515138</v>
       </c>
       <c r="CX78" s="15">
-        <v>3.5205275909665232</v>
-      </c>
-      <c r="CY78" s="17"/>
+        <v>3.330358769860581</v>
+      </c>
+      <c r="CY78" s="15">
+        <v>3.0466220975530831</v>
+      </c>
       <c r="CZ78" s="17"/>
       <c r="DA78" s="17"/>
       <c r="DB78" s="17"/>
-      <c r="DC78" s="8"/>
+      <c r="DC78" s="17"/>
       <c r="DD78" s="8"/>
       <c r="DE78" s="8"/>
       <c r="DF78" s="8"/>
@@ -13820,13 +13891,15 @@
         <v>8.9159751301488086</v>
       </c>
       <c r="CX79" s="15">
-        <v>-2.2131020696112671</v>
-      </c>
-      <c r="CY79" s="17"/>
+        <v>-1.0269985713103154</v>
+      </c>
+      <c r="CY79" s="15">
+        <v>-3.6210602779007672</v>
+      </c>
       <c r="CZ79" s="17"/>
       <c r="DA79" s="17"/>
       <c r="DB79" s="17"/>
-      <c r="DC79" s="8"/>
+      <c r="DC79" s="17"/>
       <c r="DD79" s="8"/>
       <c r="DE79" s="8"/>
       <c r="DF79" s="8"/>
@@ -14201,13 +14274,15 @@
         <v>4.6828313079560786</v>
       </c>
       <c r="CX80" s="15">
-        <v>7.5194387876929625</v>
-      </c>
-      <c r="CY80" s="17"/>
+        <v>8.1462070499582921</v>
+      </c>
+      <c r="CY80" s="15">
+        <v>-1.8752194381742413</v>
+      </c>
       <c r="CZ80" s="17"/>
       <c r="DA80" s="17"/>
       <c r="DB80" s="17"/>
-      <c r="DC80" s="8"/>
+      <c r="DC80" s="17"/>
       <c r="DD80" s="8"/>
       <c r="DE80" s="8"/>
       <c r="DF80" s="8"/>
@@ -14582,13 +14657,15 @@
         <v>4.1714281045212687</v>
       </c>
       <c r="CX81" s="15">
-        <v>3.9096779949188374</v>
-      </c>
-      <c r="CY81" s="17"/>
+        <v>4.8843585465139228</v>
+      </c>
+      <c r="CY81" s="15">
+        <v>6.2880190394676276</v>
+      </c>
       <c r="CZ81" s="17"/>
       <c r="DA81" s="17"/>
       <c r="DB81" s="17"/>
-      <c r="DC81" s="8"/>
+      <c r="DC81" s="17"/>
       <c r="DD81" s="8"/>
       <c r="DE81" s="8"/>
       <c r="DF81" s="8"/>
@@ -14963,13 +15040,15 @@
         <v>18.906792926375985</v>
       </c>
       <c r="CX82" s="15">
-        <v>14.691922901360414</v>
-      </c>
-      <c r="CY82" s="17"/>
+        <v>20.769880913456134</v>
+      </c>
+      <c r="CY82" s="15">
+        <v>25.263069327584418</v>
+      </c>
       <c r="CZ82" s="17"/>
       <c r="DA82" s="17"/>
       <c r="DB82" s="17"/>
-      <c r="DC82" s="8"/>
+      <c r="DC82" s="17"/>
       <c r="DD82" s="8"/>
       <c r="DE82" s="8"/>
       <c r="DF82" s="8"/>
@@ -15141,11 +15220,11 @@
       <c r="CV83" s="8"/>
       <c r="CW83" s="8"/>
       <c r="CX83" s="8"/>
-      <c r="CY83" s="7"/>
+      <c r="CY83" s="8"/>
       <c r="CZ83" s="7"/>
       <c r="DA83" s="7"/>
       <c r="DB83" s="7"/>
-      <c r="DC83" s="8"/>
+      <c r="DC83" s="7"/>
       <c r="DD83" s="8"/>
       <c r="DE83" s="8"/>
       <c r="DF83" s="8"/>
@@ -15520,13 +15599,15 @@
         <v>4.7935023552001468</v>
       </c>
       <c r="CX84" s="15">
-        <v>4.4163588023732103</v>
-      </c>
-      <c r="CY84" s="17"/>
+        <v>5.032718731804195</v>
+      </c>
+      <c r="CY84" s="15">
+        <v>3.8117278066116143</v>
+      </c>
       <c r="CZ84" s="17"/>
       <c r="DA84" s="17"/>
       <c r="DB84" s="17"/>
-      <c r="DC84" s="8"/>
+      <c r="DC84" s="17"/>
       <c r="DD84" s="8"/>
       <c r="DE84" s="8"/>
       <c r="DF84" s="8"/>
@@ -15699,19 +15780,20 @@
       <c r="CV85" s="10"/>
       <c r="CW85" s="10"/>
       <c r="CX85" s="10"/>
-      <c r="CY85" s="25"/>
+      <c r="CY85" s="10"/>
       <c r="CZ85" s="25"/>
       <c r="DA85" s="25"/>
       <c r="DB85" s="25"/>
+      <c r="DC85" s="25"/>
     </row>
     <row r="86" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A86" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY86" s="4"/>
       <c r="CZ86" s="4"/>
       <c r="DA86" s="4"/>
       <c r="DB86" s="4"/>
+      <c r="DC86" s="4"/>
     </row>
     <row r="87" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="8"/>
@@ -15814,12 +15896,12 @@
       <c r="CU87" s="8"/>
       <c r="CV87" s="8"/>
       <c r="CW87" s="8"/>
-      <c r="CX87" s="7"/>
-      <c r="CY87" s="7"/>
+      <c r="CX87" s="8"/>
+      <c r="CY87" s="8"/>
       <c r="CZ87" s="7"/>
       <c r="DA87" s="7"/>
       <c r="DB87" s="7"/>
-      <c r="DC87" s="8"/>
+      <c r="DC87" s="7"/>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
       <c r="DF87" s="8"/>
@@ -15990,12 +16072,12 @@
       <c r="CU88" s="8"/>
       <c r="CV88" s="8"/>
       <c r="CW88" s="8"/>
-      <c r="CX88" s="7"/>
-      <c r="CY88" s="7"/>
+      <c r="CX88" s="8"/>
+      <c r="CY88" s="8"/>
       <c r="CZ88" s="7"/>
       <c r="DA88" s="7"/>
       <c r="DB88" s="7"/>
-      <c r="DC88" s="8"/>
+      <c r="DC88" s="7"/>
       <c r="DD88" s="8"/>
       <c r="DE88" s="8"/>
       <c r="DF88" s="8"/>
@@ -16072,7 +16154,7 @@
     </row>
     <row r="90" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:175" x14ac:dyDescent="0.2">
@@ -16082,7 +16164,7 @@
     </row>
     <row r="93" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:175" x14ac:dyDescent="0.2">
@@ -16251,6 +16333,7 @@
       <c r="DB96" s="22">
         <v>2026</v>
       </c>
+      <c r="DC96" s="22"/>
     </row>
     <row r="97" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
@@ -16570,6 +16653,9 @@
       </c>
       <c r="DB97" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC97" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -16892,9 +16978,11 @@
         <v>128.22448172834294</v>
       </c>
       <c r="DB99" s="15">
-        <v>131.15744709417584</v>
-      </c>
-      <c r="DC99" s="8"/>
+        <v>131.16679820355773</v>
+      </c>
+      <c r="DC99" s="15">
+        <v>147.57075990481914</v>
+      </c>
       <c r="DD99" s="8"/>
       <c r="DE99" s="8"/>
       <c r="DF99" s="8"/>
@@ -17287,7 +17375,9 @@
       <c r="DB100" s="15">
         <v>127.39210739007146</v>
       </c>
-      <c r="DC100" s="8"/>
+      <c r="DC100" s="15">
+        <v>124.37026133412384</v>
+      </c>
       <c r="DD100" s="8"/>
       <c r="DE100" s="8"/>
       <c r="DF100" s="8"/>
@@ -17678,9 +17768,11 @@
         <v>140.1986752421644</v>
       </c>
       <c r="DB101" s="15">
-        <v>121.63325434601356</v>
-      </c>
-      <c r="DC101" s="8"/>
+        <v>119.88922551035905</v>
+      </c>
+      <c r="DC101" s="15">
+        <v>147.54380832874244</v>
+      </c>
       <c r="DD101" s="8"/>
       <c r="DE101" s="8"/>
       <c r="DF101" s="8"/>
@@ -18073,7 +18165,9 @@
       <c r="DB102" s="15">
         <v>115.5530402883532</v>
       </c>
-      <c r="DC102" s="8"/>
+      <c r="DC102" s="15">
+        <v>138.37919001574821</v>
+      </c>
       <c r="DD102" s="8"/>
       <c r="DE102" s="8"/>
       <c r="DF102" s="8"/>
@@ -18464,9 +18558,11 @@
         <v>101.7287822299658</v>
       </c>
       <c r="DB103" s="15">
-        <v>103.43537470169912</v>
-      </c>
-      <c r="DC103" s="8"/>
+        <v>103.43537470169915</v>
+      </c>
+      <c r="DC103" s="15">
+        <v>105.53091182414516</v>
+      </c>
       <c r="DD103" s="8"/>
       <c r="DE103" s="8"/>
       <c r="DF103" s="8"/>
@@ -19037,9 +19133,11 @@
         <v>127.67179385333516</v>
       </c>
       <c r="DB105" s="15">
-        <v>123.92809296996911</v>
-      </c>
-      <c r="DC105" s="8"/>
+        <v>123.58029076038441</v>
+      </c>
+      <c r="DC105" s="15">
+        <v>141.08443128056786</v>
+      </c>
       <c r="DD105" s="8"/>
       <c r="DE105" s="8"/>
       <c r="DF105" s="8"/>
@@ -19220,6 +19318,7 @@
       <c r="CZ106" s="10"/>
       <c r="DA106" s="10"/>
       <c r="DB106" s="10"/>
+      <c r="DC106" s="10"/>
     </row>
     <row r="107" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A107" s="11" t="s">
@@ -19238,7 +19337,7 @@
     </row>
     <row r="112" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" spans="1:179" x14ac:dyDescent="0.2">
@@ -19248,7 +19347,7 @@
     </row>
     <row r="115" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="116" spans="1:179" x14ac:dyDescent="0.2">
@@ -19417,6 +19516,7 @@
       <c r="DB118" s="22">
         <v>2026</v>
       </c>
+      <c r="DC118" s="22"/>
     </row>
     <row r="119" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
@@ -19736,6 +19836,9 @@
       </c>
       <c r="DB119" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC119" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20058,9 +20161,11 @@
         <v>52.487906577344013</v>
       </c>
       <c r="DB121" s="15">
-        <v>50.293943852772202</v>
-      </c>
-      <c r="DC121" s="8"/>
+        <v>50.050982517887419</v>
+      </c>
+      <c r="DC121" s="15">
+        <v>49.70723490766332</v>
+      </c>
       <c r="DD121" s="8"/>
       <c r="DE121" s="8"/>
       <c r="DF121" s="8"/>
@@ -20451,9 +20556,11 @@
         <v>4.5363569881052888</v>
       </c>
       <c r="DB122" s="15">
-        <v>5.5997447353155696</v>
-      </c>
-      <c r="DC122" s="8"/>
+        <v>5.6502646874637197</v>
+      </c>
+      <c r="DC122" s="15">
+        <v>5.5200479506228328</v>
+      </c>
       <c r="DD122" s="8"/>
       <c r="DE122" s="8"/>
       <c r="DF122" s="8"/>
@@ -20844,9 +20951,11 @@
         <v>15.414958691439375</v>
       </c>
       <c r="DB123" s="15">
-        <v>15.183070616298252</v>
-      </c>
-      <c r="DC123" s="8"/>
+        <v>15.006390193675239</v>
+      </c>
+      <c r="DC123" s="15">
+        <v>15.560317029106653</v>
+      </c>
       <c r="DD123" s="8"/>
       <c r="DE123" s="8"/>
       <c r="DF123" s="8"/>
@@ -21237,9 +21346,11 @@
         <v>23.678570725511932</v>
       </c>
       <c r="DB124" s="15">
-        <v>24.611845954670418</v>
-      </c>
-      <c r="DC124" s="8"/>
+        <v>24.766429888056273</v>
+      </c>
+      <c r="DC124" s="15">
+        <v>24.31838535159493</v>
+      </c>
       <c r="DD124" s="8"/>
       <c r="DE124" s="8"/>
       <c r="DF124" s="8"/>
@@ -21630,9 +21741,11 @@
         <v>3.8822070175993808</v>
       </c>
       <c r="DB125" s="15">
-        <v>4.311394840943569</v>
-      </c>
-      <c r="DC125" s="8"/>
+        <v>4.5259327129173519</v>
+      </c>
+      <c r="DC125" s="15">
+        <v>4.8940147610122757</v>
+      </c>
       <c r="DD125" s="8"/>
       <c r="DE125" s="8"/>
       <c r="DF125" s="8"/>
@@ -22205,7 +22318,9 @@
       <c r="DB127" s="15">
         <v>100</v>
       </c>
-      <c r="DC127" s="8"/>
+      <c r="DC127" s="15">
+        <v>100</v>
+      </c>
       <c r="DD127" s="8"/>
       <c r="DE127" s="8"/>
       <c r="DF127" s="8"/>
@@ -22386,6 +22501,7 @@
       <c r="CZ128" s="10"/>
       <c r="DA128" s="10"/>
       <c r="DB128" s="10"/>
+      <c r="DC128" s="10"/>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A129" s="11" t="s">
@@ -22764,7 +22880,7 @@
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="136" spans="1:179" x14ac:dyDescent="0.2">
@@ -22774,7 +22890,7 @@
     </row>
     <row r="137" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="1:179" x14ac:dyDescent="0.2">
@@ -22943,6 +23059,7 @@
       <c r="DB140" s="22">
         <v>2026</v>
       </c>
+      <c r="DC140" s="22"/>
     </row>
     <row r="141" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
@@ -23262,6 +23379,9 @@
       </c>
       <c r="DB141" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC141" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -23584,9 +23704,11 @@
         <v>52.261667179384908</v>
       </c>
       <c r="DB143" s="15">
-        <v>47.521758677853484</v>
-      </c>
-      <c r="DC143" s="8"/>
+        <v>47.156102436871691</v>
+      </c>
+      <c r="DC143" s="15">
+        <v>47.522401944670428</v>
+      </c>
       <c r="DD143" s="8"/>
       <c r="DE143" s="8"/>
       <c r="DF143" s="8"/>
@@ -23977,9 +24099,11 @@
         <v>4.4635394115014488</v>
       </c>
       <c r="DB144" s="15">
-        <v>5.4474778727176361</v>
-      </c>
-      <c r="DC144" s="8"/>
+        <v>5.4811979113575706</v>
+      </c>
+      <c r="DC144" s="15">
+        <v>6.2618894372412717</v>
+      </c>
       <c r="DD144" s="8"/>
       <c r="DE144" s="8"/>
       <c r="DF144" s="8"/>
@@ -24370,9 +24494,11 @@
         <v>14.037617865587629</v>
       </c>
       <c r="DB145" s="15">
-        <v>15.469527614163392</v>
-      </c>
-      <c r="DC145" s="8"/>
+        <v>15.468396392617695</v>
+      </c>
+      <c r="DC145" s="15">
+        <v>14.87909593403918</v>
+      </c>
       <c r="DD145" s="8"/>
       <c r="DE145" s="8"/>
       <c r="DF145" s="8"/>
@@ -24763,9 +24889,11 @@
         <v>24.36492284196051</v>
       </c>
       <c r="DB146" s="15">
-        <v>26.395663203855818</v>
-      </c>
-      <c r="DC146" s="8"/>
+        <v>26.486906783457055</v>
+      </c>
+      <c r="DC146" s="15">
+        <v>24.793797149708752</v>
+      </c>
       <c r="DD146" s="8"/>
       <c r="DE146" s="8"/>
       <c r="DF146" s="8"/>
@@ -25156,9 +25284,11 @@
         <v>4.8722527015655004</v>
       </c>
       <c r="DB147" s="15">
-        <v>5.1655726314096579</v>
-      </c>
-      <c r="DC147" s="8"/>
+        <v>5.4073964756959869</v>
+      </c>
+      <c r="DC147" s="15">
+        <v>6.5428155343403738</v>
+      </c>
       <c r="DD147" s="8"/>
       <c r="DE147" s="8"/>
       <c r="DF147" s="8"/>
@@ -25731,7 +25861,9 @@
       <c r="DB149" s="15">
         <v>100</v>
       </c>
-      <c r="DC149" s="8"/>
+      <c r="DC149" s="15">
+        <v>100</v>
+      </c>
       <c r="DD149" s="8"/>
       <c r="DE149" s="8"/>
       <c r="DF149" s="8"/>
@@ -25912,6 +26044,7 @@
       <c r="CZ150" s="10"/>
       <c r="DA150" s="10"/>
       <c r="DB150" s="10"/>
+      <c r="DC150" s="10"/>
     </row>
     <row r="151" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A151" s="11" t="s">
@@ -26105,9 +26238,9 @@
   <pageSetup paperSize="9" scale="29" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="44" max="105" man="1"/>
-    <brk id="88" max="105" man="1"/>
-    <brk id="109" max="105" man="1"/>
+    <brk id="44" max="106" man="1"/>
+    <brk id="88" max="106" man="1"/>
+    <brk id="109" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>